--- a/data/Navigator_GoogleSheet_Template.xlsx
+++ b/data/Navigator_GoogleSheet_Template.xlsx
@@ -581,10 +581,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -640,10 +636,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -699,10 +691,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -753,10 +741,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -812,10 +796,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -871,10 +851,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -930,10 +906,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -984,10 +956,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1043,10 +1011,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1097,10 +1061,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1156,10 +1116,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1215,10 +1171,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1274,10 +1226,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1333,10 +1281,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1392,10 +1336,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1446,10 +1386,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1500,10 +1436,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1554,10 +1486,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1608,10 +1536,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1662,10 +1586,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1716,10 +1636,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1775,10 +1691,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1834,10 +1746,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1893,10 +1801,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1952,10 +1856,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2011,10 +1911,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2070,10 +1966,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2129,10 +2021,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2188,10 +2076,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2242,10 +2126,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2296,10 +2176,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2350,10 +2226,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2404,10 +2276,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2458,10 +2326,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2512,10 +2376,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2566,10 +2426,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2620,10 +2476,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2674,10 +2526,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2728,10 +2576,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2782,10 +2626,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2836,10 +2676,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2890,10 +2726,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2944,10 +2776,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2998,10 +2826,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3052,10 +2876,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3111,10 +2931,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3165,10 +2981,6 @@
           <t>Added by M&amp;E after 15 Sep 2026 team meeting</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3219,10 +3031,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3273,10 +3081,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3327,10 +3131,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3381,10 +3181,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3435,10 +3231,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3494,10 +3286,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3548,10 +3336,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3602,10 +3386,6 @@
           <t>Implementation KPI Matrix (original plan)</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3651,10 +3431,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3700,10 +3476,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3754,10 +3526,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3808,10 +3576,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3862,10 +3626,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3911,10 +3671,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3960,10 +3716,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4014,10 +3766,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4063,10 +3811,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4112,10 +3856,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4166,10 +3906,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4220,10 +3956,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4274,10 +4006,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4328,10 +4056,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4382,10 +4106,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4436,10 +4156,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4490,10 +4206,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4544,10 +4256,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4598,10 +4306,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4652,10 +4356,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4706,10 +4406,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4760,10 +4456,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4814,10 +4506,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4863,10 +4551,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4917,10 +4601,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4971,10 +4651,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5025,10 +4701,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5079,10 +4751,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5133,10 +4801,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5187,10 +4851,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5241,10 +4901,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5295,10 +4951,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5344,10 +4996,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5398,10 +5046,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5447,10 +5091,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5501,10 +5141,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5555,10 +5191,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5609,10 +5241,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5658,10 +5286,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5712,10 +5336,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5766,10 +5386,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5815,10 +5431,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5869,10 +5481,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5918,10 +5526,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -5967,10 +5571,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6021,10 +5621,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6075,10 +5671,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6129,10 +5721,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6178,10 +5766,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6227,10 +5811,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6281,10 +5861,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6335,10 +5911,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6389,10 +5961,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6443,10 +6011,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6497,10 +6061,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6551,10 +6111,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6605,10 +6161,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6654,10 +6206,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6708,10 +6256,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6762,10 +6306,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6816,10 +6356,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6870,10 +6406,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6924,10 +6456,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -6978,10 +6506,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7032,10 +6556,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7086,10 +6606,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7140,10 +6656,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7189,10 +6701,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7243,10 +6751,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7297,10 +6801,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7351,10 +6851,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7405,10 +6901,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7459,10 +6951,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7513,10 +7001,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7567,10 +7051,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7621,10 +7101,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7675,10 +7151,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7729,10 +7201,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7783,10 +7251,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -7837,10 +7301,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -7891,10 +7351,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -7940,10 +7396,6 @@
           <t>Actual Tasks Tracker</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -7994,10 +7446,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8043,10 +7491,6 @@
           <t>Navigator Team Tracker (legacy - planned, undated)</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8092,10 +7536,6 @@
           <t>Navigator Team Tracker (legacy - planned, undated)</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8146,10 +7586,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8195,10 +7631,6 @@
           <t>Proposed by M&amp;E (derived from Project Proposal Document) - PENDING TEAM VALIDATION</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8244,10 +7676,6 @@
           <t>Proposed by M&amp;E (derived from Project Proposal Document) - PENDING TEAM VALIDATION</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8298,10 +7726,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8347,10 +7771,6 @@
           <t>Proposed by M&amp;E (derived from Project Proposal Document) - PENDING TEAM VALIDATION</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8396,10 +7816,6 @@
           <t>Proposed by M&amp;E (derived from Project Proposal Document) - PENDING TEAM VALIDATION</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8450,10 +7866,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8504,10 +7916,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8558,10 +7966,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -8607,10 +8011,6 @@
           <t>Proposed by M&amp;E (derived from Project Proposal Document) - PENDING TEAM VALIDATION</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8661,10 +8061,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8710,10 +8106,6 @@
           <t>Proposed by M&amp;E (derived from Project Proposal Document) - PENDING TEAM VALIDATION</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8759,10 +8151,6 @@
           <t>Proposed by M&amp;E (derived from Project Proposal Document) - PENDING TEAM VALIDATION</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8813,10 +8201,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8862,10 +8246,6 @@
           <t>Proposed by M&amp;E (derived from Project Proposal Document) - PENDING TEAM VALIDATION</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -8911,10 +8291,6 @@
           <t>Proposed by M&amp;E (derived from Project Proposal Document) - PENDING TEAM VALIDATION</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -8960,10 +8336,6 @@
           <t>Proposed by M&amp;E (derived from Project Proposal Document) - PENDING TEAM VALIDATION</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9014,10 +8386,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9068,10 +8436,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9122,10 +8486,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9176,10 +8536,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9230,10 +8586,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9284,10 +8636,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -9338,10 +8686,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -9392,10 +8736,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -9446,10 +8786,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -9500,10 +8836,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -9554,10 +8886,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -9608,10 +8936,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -9662,10 +8986,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -9716,10 +9036,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9770,10 +9086,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -9824,10 +9136,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -9878,10 +9186,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -9932,10 +9236,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -9986,10 +9286,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -10040,10 +9336,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -10094,10 +9386,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -10148,10 +9436,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -10202,10 +9486,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -10256,10 +9536,6 @@
           <t>Added directly by M&amp;E after 13 Sep 2026 team review (Omar/Rania/Karma work split confirmed)</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -10315,10 +9591,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -10374,10 +9646,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -10433,10 +9701,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -10487,10 +9751,6 @@
           <t>Added by M&amp;E (15 Sep 2026) - inserted to correct the Karma/Rania handoff sequence (English prep must precede English upload)</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -10541,10 +9801,6 @@
           <t>Added by M&amp;E (15 Sep 2026) - inserted to correct the Karma/Rania handoff sequence (English prep must precede English upload)</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -10595,10 +9851,6 @@
           <t>Added by M&amp;E (15 Sep 2026) - inserted to correct the Karma/Rania handoff sequence (English prep must precede English upload)</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10611,7 +9863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10859,6 +10111,33 @@
         </is>
       </c>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Maryam</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>maryam.saqer@gju.edu.jo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>843f74ee82c5d72606c3247f89ef020dceafc0344e7b1166ee4d51a152df0994</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
